--- a/data/input/Fossil Replenishment/Cluster.xlsx
+++ b/data/input/Fossil Replenishment/Cluster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F7E2068-6C25-4538-9CCF-4A3817287E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017CE957-FEAA-456C-BD6A-B529328FB879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F651F294-041D-4851-877B-E12544EA1683}"/>
   </bookViews>
@@ -469,6 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A6BF5F-698F-4409-BCD5-2245EEFFB050}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -480,7 +481,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -504,7 +505,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -512,7 +513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -520,7 +521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -528,7 +529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -536,7 +537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -544,7 +545,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -552,7 +553,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -560,7 +561,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -568,7 +569,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -584,7 +585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -600,7 +601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -624,7 +625,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -633,6 +634,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B20" xr:uid="{44A6BF5F-698F-4409-BCD5-2245EEFFB050}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="BOM"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/input/Fossil Replenishment/Cluster.xlsx
+++ b/data/input/Fossil Replenishment/Cluster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017CE957-FEAA-456C-BD6A-B529328FB879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD618441-F899-45F6-90BB-C8DBAF286152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F651F294-041D-4851-877B-E12544EA1683}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>Location</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>Cluster</t>
+  </si>
+  <si>
+    <t>DED3</t>
   </si>
 </sst>
 </file>
@@ -469,8 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A6BF5F-698F-4409-BCD5-2245EEFFB050}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -481,7 +483,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -505,7 +507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -513,7 +515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -521,7 +523,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -529,7 +531,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -537,7 +539,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -545,7 +547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -553,7 +555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -561,7 +563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -569,7 +571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -585,7 +587,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -601,7 +603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -625,7 +627,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -633,14 +635,15 @@
         <v>22</v>
       </c>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B20" xr:uid="{44A6BF5F-698F-4409-BCD5-2245EEFFB050}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="BOM"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>